--- a/frontend/public/templates/official_cases_template.xlsx
+++ b/frontend/public/templates/official_cases_template.xlsx
@@ -7,12 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="official_cases_template" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="schema_reference" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Official Cases Template" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'official_cases_template'!$A$1:$F$2</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,33 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3F6FA"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -62,28 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="00D9E2F3"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -158,46 +122,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional in schema. Defaults to 'Manila' if left blank.</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>Required. District name as text, e.g. District 1.</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>Required. Disease name as text.</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>Required. Whole number year between 2015 and 2100.</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Required. Case count. Must be 0 or greater.</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional enum. Allowed values: official, csv, excel, system, file. Default is official.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -489,316 +413,156 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>city</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>district</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>disease</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>caseClassification</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>cases</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>source</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Upload notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Manila</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>District 1</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Acute Gastroenteritis</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>official</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>- Use one row per district + disease + year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>- Avoid duplicates for the same dataset: district + disease + year must be unique.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>- datasetId is system-generated and should not be included in the file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>- Save as .xlsx or export to .csv before upload if needed.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F2"/>
-  <dataValidations count="3">
-    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole" operator="between">
-      <formula1>2015</formula1>
-      <formula2>2100</formula2>
-    </dataValidation>
-    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole" operator="greaterThanOrEqual">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"official,csv,excel,system,file"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>field</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>rules</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>datasetId</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>District 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ObjectId</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>System-generated reference to Dataset</t>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>official</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>District 1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Defaults to Manila</t>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>suspected</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>official</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>District 1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Trimmed text</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Trimmed text</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2015 to 2100</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cases</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0 or greater</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>String enum</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>official, csv, excel, system, file</t>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>probable</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>official</t>
         </is>
       </c>
     </row>
